--- a/docs/analysis/2026-08-08-ecount-item-gap-v2.xlsx
+++ b/docs/analysis/2026-08-08-ecount-item-gap-v2.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="이카운트 품목 갭" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,24 +11,41 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'이카운트 품목 갭'!$A$1:$U$345</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <color rgb="FF2563EB"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -41,22 +57,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -80,9 +96,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -446,15 +463,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U345"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
@@ -604,8 +620,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -665,7 +681,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -693,8 +709,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -754,7 +770,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -782,8 +798,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -843,7 +859,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -871,8 +887,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -932,7 +948,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -960,8 +976,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -1021,7 +1037,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1049,8 +1065,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>프라임젯</t>
@@ -1110,7 +1126,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1138,8 +1154,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -1199,7 +1215,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1227,8 +1243,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -1288,7 +1304,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1316,8 +1332,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -1377,7 +1393,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1405,8 +1421,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>바로B&amp;R</t>
@@ -1466,7 +1482,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1494,8 +1510,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -1555,7 +1571,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1583,8 +1599,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -1644,7 +1660,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1672,9 +1688,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -1729,7 +1745,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1757,8 +1773,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -1818,7 +1834,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1846,9 +1862,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -1903,7 +1919,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1931,8 +1947,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -1992,7 +2008,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2020,8 +2036,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -2081,7 +2097,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2109,8 +2125,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -2170,7 +2186,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2198,8 +2214,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -2259,7 +2275,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2287,8 +2303,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -2348,7 +2364,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2376,8 +2392,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -2437,7 +2453,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2465,8 +2481,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -2526,7 +2542,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2539,7 +2555,7 @@
           <t>아크릴 1T</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -2550,9 +2566,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -2607,7 +2623,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2635,9 +2651,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -2692,7 +2708,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2720,8 +2736,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -2781,7 +2797,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2809,8 +2825,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -2870,7 +2886,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2898,8 +2914,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -2959,7 +2975,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2987,8 +3003,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>다선정밀</t>
@@ -3048,7 +3064,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3076,8 +3092,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>다선정밀</t>
@@ -3137,7 +3153,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3165,8 +3181,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -3226,7 +3242,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3254,8 +3270,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -3315,7 +3331,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3343,8 +3359,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -3404,7 +3420,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3432,7 +3448,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n">
         <v>68000</v>
       </c>
@@ -3495,7 +3511,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3523,8 +3539,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -3584,7 +3600,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3612,8 +3628,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -3673,7 +3689,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3686,7 +3702,7 @@
           <t>윈드배너 부품- 사각베이스용 베어링</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -3697,8 +3713,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -3758,7 +3774,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3786,11 +3802,11 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
@@ -3845,7 +3861,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3873,8 +3889,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -3934,7 +3950,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3962,8 +3978,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -4023,7 +4039,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4051,8 +4067,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>운산직물</t>
@@ -4112,7 +4128,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4140,8 +4156,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -4201,7 +4217,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4229,8 +4245,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -4290,7 +4306,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4318,8 +4334,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -4379,7 +4395,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4407,8 +4423,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>다선정밀</t>
@@ -4468,7 +4484,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4496,8 +4512,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>정운교역</t>
@@ -4557,7 +4573,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4585,8 +4601,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>정운교역</t>
@@ -4646,7 +4662,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4674,8 +4690,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>정운교역</t>
@@ -4735,7 +4751,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4763,8 +4779,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>정운교역</t>
@@ -4824,7 +4840,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4852,8 +4868,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -4913,7 +4929,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4941,8 +4957,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -5002,7 +5018,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5030,8 +5046,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -5091,7 +5107,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5119,8 +5135,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -5180,7 +5196,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5208,8 +5224,8 @@
           <t>전사</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>진안알미늄</t>
@@ -5269,7 +5285,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5282,7 +5298,7 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -5293,9 +5309,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -5350,7 +5366,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5378,9 +5394,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -5435,7 +5451,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5463,9 +5479,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -5520,7 +5536,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5548,9 +5564,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -5605,7 +5621,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5633,9 +5649,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -5690,7 +5706,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5718,9 +5734,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -5775,7 +5791,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5803,8 +5819,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -5864,7 +5880,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5877,7 +5893,7 @@
           <t>윈드배너 부품- 물통용 베어링</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -5888,8 +5904,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -5949,7 +5965,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5977,9 +5993,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -6034,7 +6050,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6047,7 +6063,7 @@
           <t>포맥스 재단</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -6058,9 +6074,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -6115,7 +6131,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6143,7 +6159,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n">
         <v>1500000</v>
       </c>
@@ -6206,7 +6222,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6219,7 +6235,7 @@
           <t>장비AS</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -6230,9 +6246,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -6287,7 +6303,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6300,7 +6316,7 @@
           <t>합성지 출력</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -6311,9 +6327,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -6368,7 +6384,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6381,7 +6397,7 @@
           <t>에어간판 천갈이</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -6392,9 +6408,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -6449,7 +6465,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6477,8 +6493,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -6538,7 +6554,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6566,8 +6582,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -6627,7 +6643,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6655,8 +6671,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -6716,7 +6732,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -6729,7 +6745,7 @@
           <t>친환경현수막 출력</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -6740,9 +6756,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -6797,7 +6813,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6825,8 +6841,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>정운교역</t>
@@ -6886,7 +6902,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -6914,8 +6930,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>운산직물</t>
@@ -6975,7 +6991,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7003,8 +7019,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -7064,7 +7080,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7092,8 +7108,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -7153,7 +7169,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7181,7 +7197,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="n">
         <v>79000</v>
       </c>
@@ -7244,7 +7260,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7272,7 +7288,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n">
         <v>79000</v>
       </c>
@@ -7335,7 +7351,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7363,8 +7379,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -7424,7 +7440,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -7452,7 +7468,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n">
         <v>8800000</v>
       </c>
@@ -7515,7 +7531,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -7543,8 +7559,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -7604,7 +7620,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7632,8 +7648,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -7693,7 +7709,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7721,8 +7737,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -7782,7 +7798,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7810,8 +7826,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -7871,7 +7887,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7899,8 +7915,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -7960,7 +7976,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7988,8 +8004,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -8049,7 +8065,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8077,8 +8093,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -8138,7 +8154,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -8166,8 +8182,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>정운교역</t>
@@ -8227,7 +8243,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -8255,9 +8271,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -8312,7 +8328,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -8340,8 +8356,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -8401,7 +8417,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -8429,9 +8445,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -8486,7 +8502,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -8514,8 +8530,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -8575,7 +8591,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -8603,7 +8619,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="n">
         <v>15000000</v>
       </c>
@@ -8666,7 +8682,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -8694,8 +8710,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -8755,7 +8771,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -8783,8 +8799,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -8844,7 +8860,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -8872,8 +8888,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -8933,7 +8949,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -8961,8 +8977,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -9022,7 +9038,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9050,7 +9066,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="n"/>
       <c r="G98" s="2" t="n">
         <v>62000</v>
       </c>
@@ -9113,7 +9129,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9141,7 +9157,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n">
         <v>62000</v>
       </c>
@@ -9204,7 +9220,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -9232,8 +9248,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -9293,7 +9309,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -9321,8 +9337,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t>(주)하우사인</t>
@@ -9382,7 +9398,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9410,8 +9426,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>(주)하우사인</t>
@@ -9471,7 +9487,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -9484,7 +9500,7 @@
           <t>배너부품-몸통</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -9495,8 +9511,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
           <t>현대광고기획(배너)</t>
@@ -9556,7 +9572,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9584,8 +9600,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -9645,7 +9661,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -9673,8 +9689,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -9734,7 +9750,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9747,7 +9763,7 @@
           <t>포맥스 출력</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -9758,9 +9774,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -9815,7 +9831,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -9828,7 +9844,7 @@
           <t>A4꽂이-가로</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -9839,8 +9855,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>보영텐숀</t>
@@ -9900,7 +9916,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -9928,8 +9944,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -9989,7 +10005,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -10002,7 +10018,7 @@
           <t>A4자석액자</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -10013,8 +10029,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>보영텐숀</t>
@@ -10074,7 +10090,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -10102,9 +10118,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -10159,7 +10175,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -10187,8 +10203,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -10248,7 +10264,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -10276,8 +10292,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>다선정밀</t>
@@ -10337,7 +10353,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -10350,7 +10366,7 @@
           <t>경동화물</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -10361,9 +10377,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -10418,7 +10434,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -10431,7 +10447,7 @@
           <t>경동택배</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -10442,9 +10458,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -10499,7 +10515,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -10527,8 +10543,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -10588,7 +10604,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -10616,8 +10632,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -10677,7 +10693,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -10705,9 +10721,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -10762,7 +10778,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -10775,7 +10791,7 @@
           <t>A4꽂이-세로</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -10786,8 +10802,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>보영텐숀</t>
@@ -10847,7 +10863,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10875,9 +10891,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -10932,7 +10948,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10945,7 +10961,7 @@
           <t>납작끈</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -10956,9 +10972,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11013,7 +11029,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -11026,7 +11042,7 @@
           <t>튼튼와샤</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11037,9 +11053,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="n"/>
+      <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11094,7 +11110,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -11107,7 +11123,7 @@
           <t>반품</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11118,9 +11134,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11175,7 +11191,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -11188,7 +11204,7 @@
           <t>샘플</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11199,9 +11215,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11256,7 +11272,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -11269,7 +11285,7 @@
           <t>설치비</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11280,9 +11296,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11337,7 +11353,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -11350,7 +11366,7 @@
           <t>아크릴 4T</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -11361,9 +11377,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11418,7 +11434,7 @@
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -11426,13 +11442,13 @@
           <t>2026/08/08  오후 8:39:59</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr"/>
-      <c r="C126" s="2" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11477,13 +11493,13 @@
       <c r="R126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="n"/>
       <c r="T126" s="2" t="inlineStr">
         <is>
           <t>신설 후보</t>
         </is>
       </c>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -11496,7 +11512,7 @@
           <t>돌출간판</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr"/>
+      <c r="C127" s="3" t="n"/>
       <c r="D127" s="3" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -11507,9 +11523,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr"/>
-      <c r="G127" s="3" t="inlineStr"/>
-      <c r="H127" s="3" t="inlineStr"/>
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="3" t="n"/>
+      <c r="H127" s="3" t="n"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11564,7 +11580,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U127" s="3" t="inlineStr"/>
+      <c r="U127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -11595,8 +11611,8 @@
       <c r="F128" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="G128" s="3" t="inlineStr"/>
-      <c r="H128" s="3" t="inlineStr"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
@@ -11651,7 +11667,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U128" s="3" t="inlineStr"/>
+      <c r="U128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -11664,7 +11680,7 @@
           <t>LED 2구(KDL)</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr"/>
+      <c r="C129" s="3" t="n"/>
       <c r="D129" s="3" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11678,8 +11694,8 @@
       <c r="F129" s="3" t="n">
         <v>420</v>
       </c>
-      <c r="G129" s="3" t="inlineStr"/>
-      <c r="H129" s="3" t="inlineStr"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
@@ -11734,7 +11750,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U129" s="3" t="inlineStr"/>
+      <c r="U129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -11762,9 +11778,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr"/>
-      <c r="G130" s="3" t="inlineStr"/>
-      <c r="H130" s="3" t="inlineStr"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
       <c r="I130" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11819,7 +11835,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U130" s="3" t="inlineStr"/>
+      <c r="U130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -11832,7 +11848,7 @@
           <t>솔벤조명시트</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr"/>
+      <c r="C131" s="3" t="n"/>
       <c r="D131" s="3" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11843,9 +11859,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr"/>
-      <c r="G131" s="3" t="inlineStr"/>
-      <c r="H131" s="3" t="inlineStr"/>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="3" t="n"/>
       <c r="I131" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11900,7 +11916,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U131" s="3" t="inlineStr"/>
+      <c r="U131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -11913,7 +11929,7 @@
           <t>솔벤타공시트</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr"/>
+      <c r="C132" s="3" t="n"/>
       <c r="D132" s="3" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -11924,9 +11940,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr"/>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
       <c r="I132" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -11981,7 +11997,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U132" s="3" t="inlineStr"/>
+      <c r="U132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -12009,9 +12025,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr"/>
-      <c r="G133" s="3" t="inlineStr"/>
-      <c r="H133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12066,7 +12082,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U133" s="3" t="inlineStr"/>
+      <c r="U133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -12079,7 +12095,7 @@
           <t>각관 트러스</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr"/>
+      <c r="C134" s="3" t="n"/>
       <c r="D134" s="3" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -12090,9 +12106,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr"/>
-      <c r="G134" s="3" t="inlineStr"/>
-      <c r="H134" s="3" t="inlineStr"/>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
       <c r="I134" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12147,7 +12163,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U134" s="3" t="inlineStr"/>
+      <c r="U134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -12175,9 +12191,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr"/>
-      <c r="G135" s="3" t="inlineStr"/>
-      <c r="H135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12232,7 +12248,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U135" s="3" t="inlineStr"/>
+      <c r="U135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -12260,9 +12276,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr"/>
-      <c r="G136" s="3" t="inlineStr"/>
-      <c r="H136" s="3" t="inlineStr"/>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12317,7 +12333,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U136" s="3" t="inlineStr"/>
+      <c r="U136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -12345,9 +12361,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr"/>
-      <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr"/>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12402,7 +12418,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U137" s="3" t="inlineStr"/>
+      <c r="U137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -12430,9 +12446,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr"/>
-      <c r="G138" s="3" t="inlineStr"/>
-      <c r="H138" s="3" t="inlineStr"/>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12487,7 +12503,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U138" s="3" t="inlineStr"/>
+      <c r="U138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -12515,9 +12531,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
-      <c r="H139" s="3" t="inlineStr"/>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12572,7 +12588,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U139" s="3" t="inlineStr"/>
+      <c r="U139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -12600,9 +12616,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr"/>
-      <c r="G140" s="3" t="inlineStr"/>
-      <c r="H140" s="3" t="inlineStr"/>
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12657,7 +12673,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U140" s="3" t="inlineStr"/>
+      <c r="U140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -12670,7 +12686,7 @@
           <t>경관봉(사각)</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr"/>
+      <c r="C141" s="3" t="n"/>
       <c r="D141" s="3" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -12681,9 +12697,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr"/>
-      <c r="G141" s="3" t="inlineStr"/>
-      <c r="H141" s="3" t="inlineStr"/>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12738,7 +12754,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U141" s="3" t="inlineStr"/>
+      <c r="U141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -12766,9 +12782,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr"/>
-      <c r="G142" s="3" t="inlineStr"/>
-      <c r="H142" s="3" t="inlineStr"/>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12823,7 +12839,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U142" s="3" t="inlineStr"/>
+      <c r="U142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -12851,9 +12867,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr"/>
-      <c r="G143" s="3" t="inlineStr"/>
-      <c r="H143" s="3" t="inlineStr"/>
+      <c r="F143" s="3" t="n"/>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12908,7 +12924,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U143" s="3" t="inlineStr"/>
+      <c r="U143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -12936,9 +12952,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr"/>
-      <c r="G144" s="3" t="inlineStr"/>
-      <c r="H144" s="3" t="inlineStr"/>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -12993,7 +13009,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U144" s="3" t="inlineStr"/>
+      <c r="U144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -13021,9 +13037,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr"/>
-      <c r="G145" s="3" t="inlineStr"/>
-      <c r="H145" s="3" t="inlineStr"/>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13078,7 +13094,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U145" s="3" t="inlineStr"/>
+      <c r="U145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -13106,9 +13122,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr"/>
-      <c r="G146" s="3" t="inlineStr"/>
-      <c r="H146" s="3" t="inlineStr"/>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13163,7 +13179,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U146" s="3" t="inlineStr"/>
+      <c r="U146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -13191,9 +13207,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr"/>
-      <c r="G147" s="3" t="inlineStr"/>
-      <c r="H147" s="3" t="inlineStr"/>
+      <c r="F147" s="3" t="n"/>
+      <c r="G147" s="3" t="n"/>
+      <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13248,7 +13264,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U147" s="3" t="inlineStr"/>
+      <c r="U147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -13276,9 +13292,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr"/>
-      <c r="G148" s="3" t="inlineStr"/>
-      <c r="H148" s="3" t="inlineStr"/>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13333,7 +13349,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U148" s="3" t="inlineStr"/>
+      <c r="U148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -13361,9 +13377,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr"/>
-      <c r="G149" s="3" t="inlineStr"/>
-      <c r="H149" s="3" t="inlineStr"/>
+      <c r="F149" s="3" t="n"/>
+      <c r="G149" s="3" t="n"/>
+      <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13418,7 +13434,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U149" s="3" t="inlineStr"/>
+      <c r="U149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -13446,9 +13462,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr"/>
-      <c r="G150" s="3" t="inlineStr"/>
-      <c r="H150" s="3" t="inlineStr"/>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13503,7 +13519,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U150" s="3" t="inlineStr"/>
+      <c r="U150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -13531,9 +13547,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr"/>
-      <c r="G151" s="3" t="inlineStr"/>
-      <c r="H151" s="3" t="inlineStr"/>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
       <c r="I151" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13588,7 +13604,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U151" s="3" t="inlineStr"/>
+      <c r="U151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -13616,9 +13632,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr"/>
-      <c r="H152" s="3" t="inlineStr"/>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13673,7 +13689,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U152" s="3" t="inlineStr"/>
+      <c r="U152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -13701,9 +13717,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr"/>
-      <c r="G153" s="3" t="inlineStr"/>
-      <c r="H153" s="3" t="inlineStr"/>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13758,7 +13774,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U153" s="3" t="inlineStr"/>
+      <c r="U153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -13786,9 +13802,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr"/>
-      <c r="G154" s="3" t="inlineStr"/>
-      <c r="H154" s="3" t="inlineStr"/>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13843,7 +13859,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U154" s="3" t="inlineStr"/>
+      <c r="U154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -13871,9 +13887,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr"/>
-      <c r="G155" s="3" t="inlineStr"/>
-      <c r="H155" s="3" t="inlineStr"/>
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -13928,7 +13944,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U155" s="3" t="inlineStr"/>
+      <c r="U155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -13956,9 +13972,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr"/>
-      <c r="G156" s="3" t="inlineStr"/>
-      <c r="H156" s="3" t="inlineStr"/>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14013,7 +14029,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U156" s="3" t="inlineStr"/>
+      <c r="U156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -14041,9 +14057,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr"/>
-      <c r="G157" s="3" t="inlineStr"/>
-      <c r="H157" s="3" t="inlineStr"/>
+      <c r="F157" s="3" t="n"/>
+      <c r="G157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14098,7 +14114,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U157" s="3" t="inlineStr"/>
+      <c r="U157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -14126,9 +14142,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr"/>
-      <c r="G158" s="3" t="inlineStr"/>
-      <c r="H158" s="3" t="inlineStr"/>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14183,7 +14199,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U158" s="3" t="inlineStr"/>
+      <c r="U158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -14211,9 +14227,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr"/>
-      <c r="G159" s="3" t="inlineStr"/>
-      <c r="H159" s="3" t="inlineStr"/>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14268,7 +14284,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U159" s="3" t="inlineStr"/>
+      <c r="U159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -14296,9 +14312,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr"/>
-      <c r="G160" s="3" t="inlineStr"/>
-      <c r="H160" s="3" t="inlineStr"/>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14353,7 +14369,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U160" s="3" t="inlineStr"/>
+      <c r="U160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -14381,9 +14397,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr"/>
-      <c r="G161" s="3" t="inlineStr"/>
-      <c r="H161" s="3" t="inlineStr"/>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14438,7 +14454,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U161" s="3" t="inlineStr"/>
+      <c r="U161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -14466,9 +14482,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr"/>
-      <c r="G162" s="3" t="inlineStr"/>
-      <c r="H162" s="3" t="inlineStr"/>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14523,7 +14539,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U162" s="3" t="inlineStr"/>
+      <c r="U162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -14551,9 +14567,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr"/>
-      <c r="G163" s="3" t="inlineStr"/>
-      <c r="H163" s="3" t="inlineStr"/>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14608,7 +14624,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U163" s="3" t="inlineStr"/>
+      <c r="U163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -14636,9 +14652,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F164" s="3" t="inlineStr"/>
-      <c r="G164" s="3" t="inlineStr"/>
-      <c r="H164" s="3" t="inlineStr"/>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
       <c r="I164" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14693,7 +14709,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U164" s="3" t="inlineStr"/>
+      <c r="U164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -14721,9 +14737,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F165" s="3" t="inlineStr"/>
-      <c r="G165" s="3" t="inlineStr"/>
-      <c r="H165" s="3" t="inlineStr"/>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14778,7 +14794,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U165" s="3" t="inlineStr"/>
+      <c r="U165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -14806,9 +14822,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr"/>
-      <c r="G166" s="3" t="inlineStr"/>
-      <c r="H166" s="3" t="inlineStr"/>
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
       <c r="I166" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14863,7 +14879,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U166" s="3" t="inlineStr"/>
+      <c r="U166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -14891,9 +14907,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr"/>
-      <c r="G167" s="3" t="inlineStr"/>
-      <c r="H167" s="3" t="inlineStr"/>
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
       <c r="I167" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -14948,7 +14964,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U167" s="3" t="inlineStr"/>
+      <c r="U167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -14976,9 +14992,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr"/>
-      <c r="G168" s="3" t="inlineStr"/>
-      <c r="H168" s="3" t="inlineStr"/>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
       <c r="I168" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -15033,7 +15049,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U168" s="3" t="inlineStr"/>
+      <c r="U168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -15061,9 +15077,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F169" s="3" t="inlineStr"/>
-      <c r="G169" s="3" t="inlineStr"/>
-      <c r="H169" s="3" t="inlineStr"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -15118,7 +15134,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U169" s="3" t="inlineStr"/>
+      <c r="U169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -15146,9 +15162,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F170" s="3" t="inlineStr"/>
-      <c r="G170" s="3" t="inlineStr"/>
-      <c r="H170" s="3" t="inlineStr"/>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -15203,7 +15219,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U170" s="3" t="inlineStr"/>
+      <c r="U170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -15231,7 +15247,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr"/>
+      <c r="F171" s="3" t="n"/>
       <c r="G171" s="3" t="n">
         <v>110000</v>
       </c>
@@ -15294,7 +15310,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U171" s="3" t="inlineStr"/>
+      <c r="U171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -15322,9 +15338,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr"/>
-      <c r="G172" s="3" t="inlineStr"/>
-      <c r="H172" s="3" t="inlineStr"/>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
       <c r="I172" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -15379,7 +15395,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U172" s="3" t="inlineStr"/>
+      <c r="U172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -15407,9 +15423,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr"/>
-      <c r="G173" s="3" t="inlineStr"/>
-      <c r="H173" s="3" t="inlineStr"/>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
       <c r="I173" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -15464,7 +15480,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U173" s="3" t="inlineStr"/>
+      <c r="U173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -15492,8 +15508,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr"/>
-      <c r="G174" s="3" t="inlineStr"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
       <c r="H174" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -15553,7 +15569,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U174" s="3" t="inlineStr"/>
+      <c r="U174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -15581,8 +15597,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F175" s="3" t="inlineStr"/>
-      <c r="G175" s="3" t="inlineStr"/>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
       <c r="H175" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -15642,7 +15658,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U175" s="3" t="inlineStr"/>
+      <c r="U175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -15670,8 +15686,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr"/>
-      <c r="G176" s="3" t="inlineStr"/>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
       <c r="H176" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -15731,7 +15747,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U176" s="3" t="inlineStr"/>
+      <c r="U176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -15759,8 +15775,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr"/>
-      <c r="G177" s="3" t="inlineStr"/>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="3" t="n"/>
       <c r="H177" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -15820,7 +15836,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U177" s="3" t="inlineStr"/>
+      <c r="U177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -15848,8 +15864,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr"/>
-      <c r="G178" s="3" t="inlineStr"/>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="3" t="n"/>
       <c r="H178" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -15909,7 +15925,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U178" s="3" t="inlineStr"/>
+      <c r="U178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -15937,8 +15953,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr"/>
-      <c r="G179" s="3" t="inlineStr"/>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="3" t="n"/>
       <c r="H179" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -15998,7 +16014,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U179" s="3" t="inlineStr"/>
+      <c r="U179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -16026,8 +16042,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr"/>
-      <c r="G180" s="3" t="inlineStr"/>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="3" t="n"/>
       <c r="H180" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16087,7 +16103,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U180" s="3" t="inlineStr"/>
+      <c r="U180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -16115,8 +16131,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr"/>
-      <c r="G181" s="3" t="inlineStr"/>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="3" t="n"/>
       <c r="H181" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16176,7 +16192,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U181" s="3" t="inlineStr"/>
+      <c r="U181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -16204,8 +16220,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr"/>
-      <c r="G182" s="3" t="inlineStr"/>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
       <c r="H182" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16265,7 +16281,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U182" s="3" t="inlineStr"/>
+      <c r="U182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -16293,8 +16309,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F183" s="3" t="inlineStr"/>
-      <c r="G183" s="3" t="inlineStr"/>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="3" t="n"/>
       <c r="H183" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16354,7 +16370,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U183" s="3" t="inlineStr"/>
+      <c r="U183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -16382,8 +16398,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr"/>
-      <c r="G184" s="3" t="inlineStr"/>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="3" t="n"/>
       <c r="H184" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16443,7 +16459,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U184" s="3" t="inlineStr"/>
+      <c r="U184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -16471,8 +16487,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F185" s="3" t="inlineStr"/>
-      <c r="G185" s="3" t="inlineStr"/>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="3" t="n"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16532,7 +16548,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U185" s="3" t="inlineStr"/>
+      <c r="U185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -16560,8 +16576,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F186" s="3" t="inlineStr"/>
-      <c r="G186" s="3" t="inlineStr"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
       <c r="H186" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16621,7 +16637,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U186" s="3" t="inlineStr"/>
+      <c r="U186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -16649,8 +16665,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F187" s="3" t="inlineStr"/>
-      <c r="G187" s="3" t="inlineStr"/>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="3" t="n"/>
       <c r="H187" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16710,7 +16726,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U187" s="3" t="inlineStr"/>
+      <c r="U187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -16738,8 +16754,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F188" s="3" t="inlineStr"/>
-      <c r="G188" s="3" t="inlineStr"/>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="3" t="n"/>
       <c r="H188" s="3" t="inlineStr">
         <is>
           <t>화진물산</t>
@@ -16799,7 +16815,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U188" s="3" t="inlineStr"/>
+      <c r="U188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -16827,8 +16843,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F189" s="3" t="inlineStr"/>
-      <c r="G189" s="3" t="inlineStr"/>
+      <c r="F189" s="3" t="n"/>
+      <c r="G189" s="3" t="n"/>
       <c r="H189" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -16888,7 +16904,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U189" s="3" t="inlineStr"/>
+      <c r="U189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -16916,8 +16932,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F190" s="3" t="inlineStr"/>
-      <c r="G190" s="3" t="inlineStr"/>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="3" t="n"/>
       <c r="H190" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -16977,7 +16993,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U190" s="3" t="inlineStr"/>
+      <c r="U190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -17005,8 +17021,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F191" s="3" t="inlineStr"/>
-      <c r="G191" s="3" t="inlineStr"/>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="3" t="n"/>
       <c r="H191" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17066,7 +17082,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U191" s="3" t="inlineStr"/>
+      <c r="U191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -17094,8 +17110,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F192" s="3" t="inlineStr"/>
-      <c r="G192" s="3" t="inlineStr"/>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
       <c r="H192" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17155,7 +17171,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U192" s="3" t="inlineStr"/>
+      <c r="U192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -17183,8 +17199,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F193" s="3" t="inlineStr"/>
-      <c r="G193" s="3" t="inlineStr"/>
+      <c r="F193" s="3" t="n"/>
+      <c r="G193" s="3" t="n"/>
       <c r="H193" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17244,7 +17260,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U193" s="3" t="inlineStr"/>
+      <c r="U193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -17272,8 +17288,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F194" s="3" t="inlineStr"/>
-      <c r="G194" s="3" t="inlineStr"/>
+      <c r="F194" s="3" t="n"/>
+      <c r="G194" s="3" t="n"/>
       <c r="H194" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17333,7 +17349,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U194" s="3" t="inlineStr"/>
+      <c r="U194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -17361,8 +17377,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F195" s="3" t="inlineStr"/>
-      <c r="G195" s="3" t="inlineStr"/>
+      <c r="F195" s="3" t="n"/>
+      <c r="G195" s="3" t="n"/>
       <c r="H195" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17422,7 +17438,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U195" s="3" t="inlineStr"/>
+      <c r="U195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -17450,8 +17466,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F196" s="3" t="inlineStr"/>
-      <c r="G196" s="3" t="inlineStr"/>
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="3" t="n"/>
       <c r="H196" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17511,7 +17527,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U196" s="3" t="inlineStr"/>
+      <c r="U196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -17539,8 +17555,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F197" s="3" t="inlineStr"/>
-      <c r="G197" s="3" t="inlineStr"/>
+      <c r="F197" s="3" t="n"/>
+      <c r="G197" s="3" t="n"/>
       <c r="H197" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17600,7 +17616,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U197" s="3" t="inlineStr"/>
+      <c r="U197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -17628,8 +17644,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F198" s="3" t="inlineStr"/>
-      <c r="G198" s="3" t="inlineStr"/>
+      <c r="F198" s="3" t="n"/>
+      <c r="G198" s="3" t="n"/>
       <c r="H198" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17689,7 +17705,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U198" s="3" t="inlineStr"/>
+      <c r="U198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -17717,8 +17733,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F199" s="3" t="inlineStr"/>
-      <c r="G199" s="3" t="inlineStr"/>
+      <c r="F199" s="3" t="n"/>
+      <c r="G199" s="3" t="n"/>
       <c r="H199" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17778,7 +17794,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U199" s="3" t="inlineStr"/>
+      <c r="U199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -17806,8 +17822,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F200" s="3" t="inlineStr"/>
-      <c r="G200" s="3" t="inlineStr"/>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17867,7 +17883,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U200" s="3" t="inlineStr"/>
+      <c r="U200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -17895,8 +17911,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F201" s="3" t="inlineStr"/>
-      <c r="G201" s="3" t="inlineStr"/>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="3" t="n"/>
       <c r="H201" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -17956,7 +17972,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U201" s="3" t="inlineStr"/>
+      <c r="U201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -17984,8 +18000,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F202" s="3" t="inlineStr"/>
-      <c r="G202" s="3" t="inlineStr"/>
+      <c r="F202" s="3" t="n"/>
+      <c r="G202" s="3" t="n"/>
       <c r="H202" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -18045,7 +18061,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U202" s="3" t="inlineStr"/>
+      <c r="U202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -18073,8 +18089,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F203" s="3" t="inlineStr"/>
-      <c r="G203" s="3" t="inlineStr"/>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="3" t="n"/>
       <c r="H203" s="3" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -18134,7 +18150,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U203" s="3" t="inlineStr"/>
+      <c r="U203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -18162,8 +18178,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F204" s="3" t="inlineStr"/>
-      <c r="G204" s="3" t="inlineStr"/>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="n"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
           <t>다선정밀</t>
@@ -18223,7 +18239,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U204" s="3" t="inlineStr"/>
+      <c r="U204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -18236,7 +18252,7 @@
           <t>갈바</t>
         </is>
       </c>
-      <c r="C205" s="3" t="inlineStr"/>
+      <c r="C205" s="3" t="n"/>
       <c r="D205" s="3" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -18247,9 +18263,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr"/>
-      <c r="G205" s="3" t="inlineStr"/>
-      <c r="H205" s="3" t="inlineStr"/>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -18304,7 +18320,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U205" s="3" t="inlineStr"/>
+      <c r="U205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -18332,9 +18348,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr"/>
-      <c r="G206" s="3" t="inlineStr"/>
-      <c r="H206" s="3" t="inlineStr"/>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
       <c r="I206" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -18389,7 +18405,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U206" s="3" t="inlineStr"/>
+      <c r="U206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -18417,9 +18433,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F207" s="3" t="inlineStr"/>
-      <c r="G207" s="3" t="inlineStr"/>
-      <c r="H207" s="3" t="inlineStr"/>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -18474,7 +18490,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U207" s="3" t="inlineStr"/>
+      <c r="U207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -18502,9 +18518,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F208" s="3" t="inlineStr"/>
-      <c r="G208" s="3" t="inlineStr"/>
-      <c r="H208" s="3" t="inlineStr"/>
+      <c r="F208" s="3" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -18559,7 +18575,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U208" s="3" t="inlineStr"/>
+      <c r="U208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -18587,8 +18603,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F209" s="3" t="inlineStr"/>
-      <c r="G209" s="3" t="inlineStr"/>
+      <c r="F209" s="3" t="n"/>
+      <c r="G209" s="3" t="n"/>
       <c r="H209" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -18648,7 +18664,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U209" s="3" t="inlineStr"/>
+      <c r="U209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -18676,8 +18692,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr"/>
-      <c r="G210" s="3" t="inlineStr"/>
+      <c r="F210" s="3" t="n"/>
+      <c r="G210" s="3" t="n"/>
       <c r="H210" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -18737,7 +18753,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U210" s="3" t="inlineStr"/>
+      <c r="U210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -18765,9 +18781,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F211" s="3" t="inlineStr"/>
-      <c r="G211" s="3" t="inlineStr"/>
-      <c r="H211" s="3" t="inlineStr"/>
+      <c r="F211" s="3" t="n"/>
+      <c r="G211" s="3" t="n"/>
+      <c r="H211" s="3" t="n"/>
       <c r="I211" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -18822,7 +18838,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U211" s="3" t="inlineStr"/>
+      <c r="U211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -18850,7 +18866,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr"/>
+      <c r="F212" s="3" t="n"/>
       <c r="G212" s="3" t="n">
         <v>27000</v>
       </c>
@@ -18913,7 +18929,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U212" s="3" t="inlineStr"/>
+      <c r="U212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -18941,7 +18957,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F213" s="3" t="inlineStr"/>
+      <c r="F213" s="3" t="n"/>
       <c r="G213" s="3" t="n">
         <v>71500</v>
       </c>
@@ -19004,7 +19020,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U213" s="3" t="inlineStr"/>
+      <c r="U213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -19032,8 +19048,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F214" s="3" t="inlineStr"/>
-      <c r="G214" s="3" t="inlineStr"/>
+      <c r="F214" s="3" t="n"/>
+      <c r="G214" s="3" t="n"/>
       <c r="H214" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19093,7 +19109,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U214" s="3" t="inlineStr"/>
+      <c r="U214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -19121,8 +19137,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F215" s="3" t="inlineStr"/>
-      <c r="G215" s="3" t="inlineStr"/>
+      <c r="F215" s="3" t="n"/>
+      <c r="G215" s="3" t="n"/>
       <c r="H215" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19182,7 +19198,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U215" s="3" t="inlineStr"/>
+      <c r="U215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -19210,8 +19226,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr"/>
-      <c r="G216" s="3" t="inlineStr"/>
+      <c r="F216" s="3" t="n"/>
+      <c r="G216" s="3" t="n"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19271,7 +19287,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U216" s="3" t="inlineStr"/>
+      <c r="U216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -19299,8 +19315,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F217" s="3" t="inlineStr"/>
-      <c r="G217" s="3" t="inlineStr"/>
+      <c r="F217" s="3" t="n"/>
+      <c r="G217" s="3" t="n"/>
       <c r="H217" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19360,7 +19376,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U217" s="3" t="inlineStr"/>
+      <c r="U217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -19388,8 +19404,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F218" s="3" t="inlineStr"/>
-      <c r="G218" s="3" t="inlineStr"/>
+      <c r="F218" s="3" t="n"/>
+      <c r="G218" s="3" t="n"/>
       <c r="H218" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19449,7 +19465,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U218" s="3" t="inlineStr"/>
+      <c r="U218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -19477,8 +19493,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F219" s="3" t="inlineStr"/>
-      <c r="G219" s="3" t="inlineStr"/>
+      <c r="F219" s="3" t="n"/>
+      <c r="G219" s="3" t="n"/>
       <c r="H219" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19538,7 +19554,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U219" s="3" t="inlineStr"/>
+      <c r="U219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -19566,8 +19582,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F220" s="3" t="inlineStr"/>
-      <c r="G220" s="3" t="inlineStr"/>
+      <c r="F220" s="3" t="n"/>
+      <c r="G220" s="3" t="n"/>
       <c r="H220" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19627,7 +19643,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U220" s="3" t="inlineStr"/>
+      <c r="U220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -19655,8 +19671,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F221" s="3" t="inlineStr"/>
-      <c r="G221" s="3" t="inlineStr"/>
+      <c r="F221" s="3" t="n"/>
+      <c r="G221" s="3" t="n"/>
       <c r="H221" s="3" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -19716,7 +19732,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U221" s="3" t="inlineStr"/>
+      <c r="U221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -19744,8 +19760,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F222" s="3" t="inlineStr"/>
-      <c r="G222" s="3" t="inlineStr"/>
+      <c r="F222" s="3" t="n"/>
+      <c r="G222" s="3" t="n"/>
       <c r="H222" s="3" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -19805,7 +19821,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U222" s="3" t="inlineStr"/>
+      <c r="U222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -19833,8 +19849,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F223" s="3" t="inlineStr"/>
-      <c r="G223" s="3" t="inlineStr"/>
+      <c r="F223" s="3" t="n"/>
+      <c r="G223" s="3" t="n"/>
       <c r="H223" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -19894,7 +19910,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U223" s="3" t="inlineStr"/>
+      <c r="U223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -19922,8 +19938,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F224" s="3" t="inlineStr"/>
-      <c r="G224" s="3" t="inlineStr"/>
+      <c r="F224" s="3" t="n"/>
+      <c r="G224" s="3" t="n"/>
       <c r="H224" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -19983,7 +19999,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U224" s="3" t="inlineStr"/>
+      <c r="U224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -20011,8 +20027,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F225" s="3" t="inlineStr"/>
-      <c r="G225" s="3" t="inlineStr"/>
+      <c r="F225" s="3" t="n"/>
+      <c r="G225" s="3" t="n"/>
       <c r="H225" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -20072,7 +20088,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U225" s="3" t="inlineStr"/>
+      <c r="U225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -20100,8 +20116,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F226" s="3" t="inlineStr"/>
-      <c r="G226" s="3" t="inlineStr"/>
+      <c r="F226" s="3" t="n"/>
+      <c r="G226" s="3" t="n"/>
       <c r="H226" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -20161,7 +20177,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U226" s="3" t="inlineStr"/>
+      <c r="U226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -20189,8 +20205,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F227" s="3" t="inlineStr"/>
-      <c r="G227" s="3" t="inlineStr"/>
+      <c r="F227" s="3" t="n"/>
+      <c r="G227" s="3" t="n"/>
       <c r="H227" s="3" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -20250,7 +20266,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U227" s="3" t="inlineStr"/>
+      <c r="U227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -20278,9 +20294,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F228" s="3" t="inlineStr"/>
-      <c r="G228" s="3" t="inlineStr"/>
-      <c r="H228" s="3" t="inlineStr"/>
+      <c r="F228" s="3" t="n"/>
+      <c r="G228" s="3" t="n"/>
+      <c r="H228" s="3" t="n"/>
       <c r="I228" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20335,7 +20351,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U228" s="3" t="inlineStr"/>
+      <c r="U228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -20363,8 +20379,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F229" s="3" t="inlineStr"/>
-      <c r="G229" s="3" t="inlineStr"/>
+      <c r="F229" s="3" t="n"/>
+      <c r="G229" s="3" t="n"/>
       <c r="H229" s="3" t="inlineStr">
         <is>
           <t>조광미디어</t>
@@ -20424,7 +20440,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U229" s="3" t="inlineStr"/>
+      <c r="U229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -20452,9 +20468,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F230" s="3" t="inlineStr"/>
-      <c r="G230" s="3" t="inlineStr"/>
-      <c r="H230" s="3" t="inlineStr"/>
+      <c r="F230" s="3" t="n"/>
+      <c r="G230" s="3" t="n"/>
+      <c r="H230" s="3" t="n"/>
       <c r="I230" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20509,7 +20525,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U230" s="3" t="inlineStr"/>
+      <c r="U230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -20537,9 +20553,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F231" s="3" t="inlineStr"/>
-      <c r="G231" s="3" t="inlineStr"/>
-      <c r="H231" s="3" t="inlineStr"/>
+      <c r="F231" s="3" t="n"/>
+      <c r="G231" s="3" t="n"/>
+      <c r="H231" s="3" t="n"/>
       <c r="I231" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20594,7 +20610,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U231" s="3" t="inlineStr"/>
+      <c r="U231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -20622,9 +20638,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F232" s="3" t="inlineStr"/>
-      <c r="G232" s="3" t="inlineStr"/>
-      <c r="H232" s="3" t="inlineStr"/>
+      <c r="F232" s="3" t="n"/>
+      <c r="G232" s="3" t="n"/>
+      <c r="H232" s="3" t="n"/>
       <c r="I232" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20679,7 +20695,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U232" s="3" t="inlineStr"/>
+      <c r="U232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -20707,9 +20723,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F233" s="3" t="inlineStr"/>
-      <c r="G233" s="3" t="inlineStr"/>
-      <c r="H233" s="3" t="inlineStr"/>
+      <c r="F233" s="3" t="n"/>
+      <c r="G233" s="3" t="n"/>
+      <c r="H233" s="3" t="n"/>
       <c r="I233" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20764,7 +20780,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U233" s="3" t="inlineStr"/>
+      <c r="U233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -20792,9 +20808,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F234" s="3" t="inlineStr"/>
-      <c r="G234" s="3" t="inlineStr"/>
-      <c r="H234" s="3" t="inlineStr"/>
+      <c r="F234" s="3" t="n"/>
+      <c r="G234" s="3" t="n"/>
+      <c r="H234" s="3" t="n"/>
       <c r="I234" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20849,7 +20865,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U234" s="3" t="inlineStr"/>
+      <c r="U234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -20877,9 +20893,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F235" s="3" t="inlineStr"/>
-      <c r="G235" s="3" t="inlineStr"/>
-      <c r="H235" s="3" t="inlineStr"/>
+      <c r="F235" s="3" t="n"/>
+      <c r="G235" s="3" t="n"/>
+      <c r="H235" s="3" t="n"/>
       <c r="I235" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -20934,7 +20950,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U235" s="3" t="inlineStr"/>
+      <c r="U235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -20962,9 +20978,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F236" s="3" t="inlineStr"/>
-      <c r="G236" s="3" t="inlineStr"/>
-      <c r="H236" s="3" t="inlineStr"/>
+      <c r="F236" s="3" t="n"/>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="3" t="n"/>
       <c r="I236" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21019,7 +21035,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U236" s="3" t="inlineStr"/>
+      <c r="U236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -21047,8 +21063,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F237" s="3" t="inlineStr"/>
-      <c r="G237" s="3" t="inlineStr"/>
+      <c r="F237" s="3" t="n"/>
+      <c r="G237" s="3" t="n"/>
       <c r="H237" s="3" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -21108,7 +21124,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U237" s="3" t="inlineStr"/>
+      <c r="U237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -21136,9 +21152,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F238" s="3" t="inlineStr"/>
-      <c r="G238" s="3" t="inlineStr"/>
-      <c r="H238" s="3" t="inlineStr"/>
+      <c r="F238" s="3" t="n"/>
+      <c r="G238" s="3" t="n"/>
+      <c r="H238" s="3" t="n"/>
       <c r="I238" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21193,7 +21209,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U238" s="3" t="inlineStr"/>
+      <c r="U238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -21221,9 +21237,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F239" s="3" t="inlineStr"/>
-      <c r="G239" s="3" t="inlineStr"/>
-      <c r="H239" s="3" t="inlineStr"/>
+      <c r="F239" s="3" t="n"/>
+      <c r="G239" s="3" t="n"/>
+      <c r="H239" s="3" t="n"/>
       <c r="I239" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21278,7 +21294,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U239" s="3" t="inlineStr"/>
+      <c r="U239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -21306,9 +21322,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F240" s="3" t="inlineStr"/>
-      <c r="G240" s="3" t="inlineStr"/>
-      <c r="H240" s="3" t="inlineStr"/>
+      <c r="F240" s="3" t="n"/>
+      <c r="G240" s="3" t="n"/>
+      <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21363,7 +21379,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U240" s="3" t="inlineStr"/>
+      <c r="U240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -21391,9 +21407,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F241" s="3" t="inlineStr"/>
-      <c r="G241" s="3" t="inlineStr"/>
-      <c r="H241" s="3" t="inlineStr"/>
+      <c r="F241" s="3" t="n"/>
+      <c r="G241" s="3" t="n"/>
+      <c r="H241" s="3" t="n"/>
       <c r="I241" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21448,7 +21464,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U241" s="3" t="inlineStr"/>
+      <c r="U241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -21476,9 +21492,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F242" s="3" t="inlineStr"/>
-      <c r="G242" s="3" t="inlineStr"/>
-      <c r="H242" s="3" t="inlineStr"/>
+      <c r="F242" s="3" t="n"/>
+      <c r="G242" s="3" t="n"/>
+      <c r="H242" s="3" t="n"/>
       <c r="I242" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21533,7 +21549,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U242" s="3" t="inlineStr"/>
+      <c r="U242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -21561,9 +21577,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F243" s="3" t="inlineStr"/>
-      <c r="G243" s="3" t="inlineStr"/>
-      <c r="H243" s="3" t="inlineStr"/>
+      <c r="F243" s="3" t="n"/>
+      <c r="G243" s="3" t="n"/>
+      <c r="H243" s="3" t="n"/>
       <c r="I243" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21618,7 +21634,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U243" s="3" t="inlineStr"/>
+      <c r="U243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -21646,9 +21662,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F244" s="3" t="inlineStr"/>
-      <c r="G244" s="3" t="inlineStr"/>
-      <c r="H244" s="3" t="inlineStr"/>
+      <c r="F244" s="3" t="n"/>
+      <c r="G244" s="3" t="n"/>
+      <c r="H244" s="3" t="n"/>
       <c r="I244" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21703,7 +21719,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U244" s="3" t="inlineStr"/>
+      <c r="U244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -21731,9 +21747,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F245" s="3" t="inlineStr"/>
-      <c r="G245" s="3" t="inlineStr"/>
-      <c r="H245" s="3" t="inlineStr"/>
+      <c r="F245" s="3" t="n"/>
+      <c r="G245" s="3" t="n"/>
+      <c r="H245" s="3" t="n"/>
       <c r="I245" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21788,7 +21804,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U245" s="3" t="inlineStr"/>
+      <c r="U245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
@@ -21816,8 +21832,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F246" s="3" t="inlineStr"/>
-      <c r="G246" s="3" t="inlineStr"/>
+      <c r="F246" s="3" t="n"/>
+      <c r="G246" s="3" t="n"/>
       <c r="H246" s="3" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -21877,7 +21893,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U246" s="3" t="inlineStr"/>
+      <c r="U246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -21905,9 +21921,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F247" s="3" t="inlineStr"/>
-      <c r="G247" s="3" t="inlineStr"/>
-      <c r="H247" s="3" t="inlineStr"/>
+      <c r="F247" s="3" t="n"/>
+      <c r="G247" s="3" t="n"/>
+      <c r="H247" s="3" t="n"/>
       <c r="I247" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -21962,7 +21978,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U247" s="3" t="inlineStr"/>
+      <c r="U247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -21990,7 +22006,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F248" s="3" t="inlineStr"/>
+      <c r="F248" s="3" t="n"/>
       <c r="G248" s="3" t="n">
         <v>58200</v>
       </c>
@@ -22053,7 +22069,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U248" s="3" t="inlineStr"/>
+      <c r="U248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -22081,7 +22097,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F249" s="3" t="inlineStr"/>
+      <c r="F249" s="3" t="n"/>
       <c r="G249" s="3" t="n">
         <v>79000</v>
       </c>
@@ -22144,7 +22160,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U249" s="3" t="inlineStr"/>
+      <c r="U249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -22172,7 +22188,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F250" s="3" t="inlineStr"/>
+      <c r="F250" s="3" t="n"/>
       <c r="G250" s="3" t="n">
         <v>93500</v>
       </c>
@@ -22235,7 +22251,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U250" s="3" t="inlineStr"/>
+      <c r="U250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -22263,7 +22279,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F251" s="3" t="inlineStr"/>
+      <c r="F251" s="3" t="n"/>
       <c r="G251" s="3" t="n">
         <v>58200</v>
       </c>
@@ -22326,7 +22342,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U251" s="3" t="inlineStr"/>
+      <c r="U251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -22354,7 +22370,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F252" s="3" t="inlineStr"/>
+      <c r="F252" s="3" t="n"/>
       <c r="G252" s="3" t="n">
         <v>79000</v>
       </c>
@@ -22417,7 +22433,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U252" s="3" t="inlineStr"/>
+      <c r="U252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -22445,7 +22461,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F253" s="3" t="inlineStr"/>
+      <c r="F253" s="3" t="n"/>
       <c r="G253" s="3" t="n">
         <v>93500</v>
       </c>
@@ -22508,7 +22524,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U253" s="3" t="inlineStr"/>
+      <c r="U253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -22536,8 +22552,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F254" s="3" t="inlineStr"/>
-      <c r="G254" s="3" t="inlineStr"/>
+      <c r="F254" s="3" t="n"/>
+      <c r="G254" s="3" t="n"/>
       <c r="H254" s="3" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -22597,7 +22613,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U254" s="3" t="inlineStr"/>
+      <c r="U254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -22625,8 +22641,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F255" s="3" t="inlineStr"/>
-      <c r="G255" s="3" t="inlineStr"/>
+      <c r="F255" s="3" t="n"/>
+      <c r="G255" s="3" t="n"/>
       <c r="H255" s="3" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -22686,7 +22702,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U255" s="3" t="inlineStr"/>
+      <c r="U255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -22714,8 +22730,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F256" s="3" t="inlineStr"/>
-      <c r="G256" s="3" t="inlineStr"/>
+      <c r="F256" s="3" t="n"/>
+      <c r="G256" s="3" t="n"/>
       <c r="H256" s="3" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -22775,7 +22791,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U256" s="3" t="inlineStr"/>
+      <c r="U256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -22803,8 +22819,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F257" s="3" t="inlineStr"/>
-      <c r="G257" s="3" t="inlineStr"/>
+      <c r="F257" s="3" t="n"/>
+      <c r="G257" s="3" t="n"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -22864,7 +22880,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U257" s="3" t="inlineStr"/>
+      <c r="U257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -22892,8 +22908,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F258" s="3" t="inlineStr"/>
-      <c r="G258" s="3" t="inlineStr"/>
+      <c r="F258" s="3" t="n"/>
+      <c r="G258" s="3" t="n"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
           <t>프라임젯</t>
@@ -22953,7 +22969,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U258" s="3" t="inlineStr"/>
+      <c r="U258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -22981,9 +22997,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F259" s="3" t="inlineStr"/>
-      <c r="G259" s="3" t="inlineStr"/>
-      <c r="H259" s="3" t="inlineStr"/>
+      <c r="F259" s="3" t="n"/>
+      <c r="G259" s="3" t="n"/>
+      <c r="H259" s="3" t="n"/>
       <c r="I259" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23038,7 +23054,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U259" s="3" t="inlineStr"/>
+      <c r="U259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -23066,8 +23082,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F260" s="3" t="inlineStr"/>
-      <c r="G260" s="3" t="inlineStr"/>
+      <c r="F260" s="3" t="n"/>
+      <c r="G260" s="3" t="n"/>
       <c r="H260" s="3" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -23127,7 +23143,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U260" s="3" t="inlineStr"/>
+      <c r="U260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -23155,8 +23171,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F261" s="3" t="inlineStr"/>
-      <c r="G261" s="3" t="inlineStr"/>
+      <c r="F261" s="3" t="n"/>
+      <c r="G261" s="3" t="n"/>
       <c r="H261" s="3" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -23216,7 +23232,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U261" s="3" t="inlineStr"/>
+      <c r="U261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -23244,8 +23260,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F262" s="3" t="inlineStr"/>
-      <c r="G262" s="3" t="inlineStr"/>
+      <c r="F262" s="3" t="n"/>
+      <c r="G262" s="3" t="n"/>
       <c r="H262" s="3" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -23305,7 +23321,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U262" s="3" t="inlineStr"/>
+      <c r="U262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -23333,8 +23349,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F263" s="3" t="inlineStr"/>
-      <c r="G263" s="3" t="inlineStr"/>
+      <c r="F263" s="3" t="n"/>
+      <c r="G263" s="3" t="n"/>
       <c r="H263" s="3" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -23394,7 +23410,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U263" s="3" t="inlineStr"/>
+      <c r="U263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -23422,8 +23438,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F264" s="3" t="inlineStr"/>
-      <c r="G264" s="3" t="inlineStr"/>
+      <c r="F264" s="3" t="n"/>
+      <c r="G264" s="3" t="n"/>
       <c r="H264" s="3" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -23483,7 +23499,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U264" s="3" t="inlineStr"/>
+      <c r="U264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -23511,9 +23527,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F265" s="3" t="inlineStr"/>
-      <c r="G265" s="3" t="inlineStr"/>
-      <c r="H265" s="3" t="inlineStr"/>
+      <c r="F265" s="3" t="n"/>
+      <c r="G265" s="3" t="n"/>
+      <c r="H265" s="3" t="n"/>
       <c r="I265" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23568,7 +23584,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U265" s="3" t="inlineStr"/>
+      <c r="U265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -23596,9 +23612,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F266" s="3" t="inlineStr"/>
-      <c r="G266" s="3" t="inlineStr"/>
-      <c r="H266" s="3" t="inlineStr"/>
+      <c r="F266" s="3" t="n"/>
+      <c r="G266" s="3" t="n"/>
+      <c r="H266" s="3" t="n"/>
       <c r="I266" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23653,7 +23669,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U266" s="3" t="inlineStr"/>
+      <c r="U266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -23681,9 +23697,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F267" s="3" t="inlineStr"/>
-      <c r="G267" s="3" t="inlineStr"/>
-      <c r="H267" s="3" t="inlineStr"/>
+      <c r="F267" s="3" t="n"/>
+      <c r="G267" s="3" t="n"/>
+      <c r="H267" s="3" t="n"/>
       <c r="I267" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23738,7 +23754,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U267" s="3" t="inlineStr"/>
+      <c r="U267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -23766,9 +23782,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F268" s="3" t="inlineStr"/>
-      <c r="G268" s="3" t="inlineStr"/>
-      <c r="H268" s="3" t="inlineStr"/>
+      <c r="F268" s="3" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="3" t="n"/>
       <c r="I268" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23823,7 +23839,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U268" s="3" t="inlineStr"/>
+      <c r="U268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -23851,9 +23867,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F269" s="3" t="inlineStr"/>
-      <c r="G269" s="3" t="inlineStr"/>
-      <c r="H269" s="3" t="inlineStr"/>
+      <c r="F269" s="3" t="n"/>
+      <c r="G269" s="3" t="n"/>
+      <c r="H269" s="3" t="n"/>
       <c r="I269" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23908,7 +23924,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U269" s="3" t="inlineStr"/>
+      <c r="U269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -23936,9 +23952,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F270" s="3" t="inlineStr"/>
-      <c r="G270" s="3" t="inlineStr"/>
-      <c r="H270" s="3" t="inlineStr"/>
+      <c r="F270" s="3" t="n"/>
+      <c r="G270" s="3" t="n"/>
+      <c r="H270" s="3" t="n"/>
       <c r="I270" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -23993,7 +24009,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U270" s="3" t="inlineStr"/>
+      <c r="U270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -24021,9 +24037,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F271" s="3" t="inlineStr"/>
-      <c r="G271" s="3" t="inlineStr"/>
-      <c r="H271" s="3" t="inlineStr"/>
+      <c r="F271" s="3" t="n"/>
+      <c r="G271" s="3" t="n"/>
+      <c r="H271" s="3" t="n"/>
       <c r="I271" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24078,7 +24094,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U271" s="3" t="inlineStr"/>
+      <c r="U271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -24106,9 +24122,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F272" s="3" t="inlineStr"/>
-      <c r="G272" s="3" t="inlineStr"/>
-      <c r="H272" s="3" t="inlineStr"/>
+      <c r="F272" s="3" t="n"/>
+      <c r="G272" s="3" t="n"/>
+      <c r="H272" s="3" t="n"/>
       <c r="I272" s="3" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24163,7 +24179,7 @@
           <t>기존연결 유력</t>
         </is>
       </c>
-      <c r="U272" s="3" t="inlineStr"/>
+      <c r="U272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -24176,7 +24192,7 @@
           <t>윈드배너 부품- 크로스베이스용 베어링</t>
         </is>
       </c>
-      <c r="C273" s="4" t="inlineStr"/>
+      <c r="C273" s="4" t="n"/>
       <c r="D273" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -24187,8 +24203,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F273" s="4" t="inlineStr"/>
-      <c r="G273" s="4" t="inlineStr"/>
+      <c r="F273" s="4" t="n"/>
+      <c r="G273" s="4" t="n"/>
       <c r="H273" s="4" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -24248,7 +24264,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U273" s="4" t="inlineStr"/>
+      <c r="U273" s="4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -24276,9 +24296,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F274" s="4" t="inlineStr"/>
-      <c r="G274" s="4" t="inlineStr"/>
-      <c r="H274" s="4" t="inlineStr"/>
+      <c r="F274" s="4" t="n"/>
+      <c r="G274" s="4" t="n"/>
+      <c r="H274" s="4" t="n"/>
       <c r="I274" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24333,7 +24353,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U274" s="4" t="inlineStr"/>
+      <c r="U274" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -24361,9 +24385,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F275" s="4" t="inlineStr"/>
-      <c r="G275" s="4" t="inlineStr"/>
-      <c r="H275" s="4" t="inlineStr"/>
+      <c r="F275" s="4" t="n"/>
+      <c r="G275" s="4" t="n"/>
+      <c r="H275" s="4" t="n"/>
       <c r="I275" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24418,7 +24442,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U275" s="4" t="inlineStr"/>
+      <c r="U275" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -24446,8 +24474,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F276" s="4" t="inlineStr"/>
-      <c r="G276" s="4" t="inlineStr"/>
+      <c r="F276" s="4" t="n"/>
+      <c r="G276" s="4" t="n"/>
       <c r="H276" s="4" t="inlineStr">
         <is>
           <t>호홍 주식회사</t>
@@ -24507,7 +24535,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U276" s="4" t="inlineStr"/>
+      <c r="U276" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -24535,8 +24567,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F277" s="4" t="inlineStr"/>
-      <c r="G277" s="4" t="inlineStr"/>
+      <c r="F277" s="4" t="n"/>
+      <c r="G277" s="4" t="n"/>
       <c r="H277" s="4" t="inlineStr">
         <is>
           <t>호홍 주식회사</t>
@@ -24596,7 +24628,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U277" s="4" t="inlineStr"/>
+      <c r="U277" s="5" t="inlineStr">
+        <is>
+          <t>HJ-YGILB-P127</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -24624,9 +24660,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F278" s="4" t="inlineStr"/>
-      <c r="G278" s="4" t="inlineStr"/>
-      <c r="H278" s="4" t="inlineStr"/>
+      <c r="F278" s="4" t="n"/>
+      <c r="G278" s="4" t="n"/>
+      <c r="H278" s="4" t="n"/>
       <c r="I278" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24681,7 +24717,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U278" s="4" t="inlineStr"/>
+      <c r="U278" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -24709,9 +24749,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F279" s="4" t="inlineStr"/>
-      <c r="G279" s="4" t="inlineStr"/>
-      <c r="H279" s="4" t="inlineStr"/>
+      <c r="F279" s="4" t="n"/>
+      <c r="G279" s="4" t="n"/>
+      <c r="H279" s="4" t="n"/>
       <c r="I279" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24766,7 +24806,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U279" s="4" t="inlineStr"/>
+      <c r="U279" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -24794,9 +24838,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F280" s="4" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr"/>
-      <c r="H280" s="4" t="inlineStr"/>
+      <c r="F280" s="4" t="n"/>
+      <c r="G280" s="4" t="n"/>
+      <c r="H280" s="4" t="n"/>
       <c r="I280" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24851,7 +24895,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U280" s="4" t="inlineStr"/>
+      <c r="U280" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -24879,9 +24927,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F281" s="4" t="inlineStr"/>
-      <c r="G281" s="4" t="inlineStr"/>
-      <c r="H281" s="4" t="inlineStr"/>
+      <c r="F281" s="4" t="n"/>
+      <c r="G281" s="4" t="n"/>
+      <c r="H281" s="4" t="n"/>
       <c r="I281" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -24936,7 +24984,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U281" s="4" t="inlineStr"/>
+      <c r="U281" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -24949,7 +25001,7 @@
           <t>광확산PC3T</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr"/>
+      <c r="C282" s="4" t="n"/>
       <c r="D282" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -24960,9 +25012,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F282" s="4" t="inlineStr"/>
-      <c r="G282" s="4" t="inlineStr"/>
-      <c r="H282" s="4" t="inlineStr"/>
+      <c r="F282" s="4" t="n"/>
+      <c r="G282" s="4" t="n"/>
+      <c r="H282" s="4" t="n"/>
       <c r="I282" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -25017,7 +25069,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U282" s="4" t="inlineStr"/>
+      <c r="U282" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -25030,7 +25086,7 @@
           <t>광확산PC5T</t>
         </is>
       </c>
-      <c r="C283" s="4" t="inlineStr"/>
+      <c r="C283" s="4" t="n"/>
       <c r="D283" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -25041,9 +25097,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F283" s="4" t="inlineStr"/>
-      <c r="G283" s="4" t="inlineStr"/>
-      <c r="H283" s="4" t="inlineStr"/>
+      <c r="F283" s="4" t="n"/>
+      <c r="G283" s="4" t="n"/>
+      <c r="H283" s="4" t="n"/>
       <c r="I283" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -25098,7 +25154,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U283" s="4" t="inlineStr"/>
+      <c r="U283" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -25126,8 +25186,8 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F284" s="4" t="inlineStr"/>
-      <c r="G284" s="4" t="inlineStr"/>
+      <c r="F284" s="4" t="n"/>
+      <c r="G284" s="4" t="n"/>
       <c r="H284" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -25187,7 +25247,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U284" s="4" t="inlineStr"/>
+      <c r="U284" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -25218,8 +25282,8 @@
       <c r="F285" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="G285" s="4" t="inlineStr"/>
-      <c r="H285" s="4" t="inlineStr"/>
+      <c r="G285" s="4" t="n"/>
+      <c r="H285" s="4" t="n"/>
       <c r="I285" s="4" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
@@ -25274,7 +25338,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U285" s="4" t="inlineStr"/>
+      <c r="U285" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -25305,8 +25373,8 @@
       <c r="F286" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="G286" s="4" t="inlineStr"/>
-      <c r="H286" s="4" t="inlineStr"/>
+      <c r="G286" s="4" t="n"/>
+      <c r="H286" s="4" t="n"/>
       <c r="I286" s="4" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
@@ -25361,7 +25429,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U286" s="4" t="inlineStr"/>
+      <c r="U286" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -25389,9 +25461,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F287" s="4" t="inlineStr"/>
-      <c r="G287" s="4" t="inlineStr"/>
-      <c r="H287" s="4" t="inlineStr"/>
+      <c r="F287" s="4" t="n"/>
+      <c r="G287" s="4" t="n"/>
+      <c r="H287" s="4" t="n"/>
       <c r="I287" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -25446,7 +25518,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U287" s="4" t="inlineStr"/>
+      <c r="U287" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -25474,9 +25550,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F288" s="4" t="inlineStr"/>
-      <c r="G288" s="4" t="inlineStr"/>
-      <c r="H288" s="4" t="inlineStr"/>
+      <c r="F288" s="4" t="n"/>
+      <c r="G288" s="4" t="n"/>
+      <c r="H288" s="4" t="n"/>
       <c r="I288" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -25531,7 +25607,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U288" s="4" t="inlineStr"/>
+      <c r="U288" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -25559,7 +25639,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F289" s="4" t="inlineStr"/>
+      <c r="F289" s="4" t="n"/>
       <c r="G289" s="4" t="n">
         <v>83000</v>
       </c>
@@ -25622,7 +25702,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U289" s="4" t="inlineStr"/>
+      <c r="U289" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -25650,8 +25734,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F290" s="4" t="inlineStr"/>
-      <c r="G290" s="4" t="inlineStr"/>
+      <c r="F290" s="4" t="n"/>
+      <c r="G290" s="4" t="n"/>
       <c r="H290" s="4" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -25711,7 +25795,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U290" s="4" t="inlineStr"/>
+      <c r="U290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -25739,8 +25823,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F291" s="4" t="inlineStr"/>
-      <c r="G291" s="4" t="inlineStr"/>
+      <c r="F291" s="4" t="n"/>
+      <c r="G291" s="4" t="n"/>
       <c r="H291" s="4" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -25800,7 +25884,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U291" s="4" t="inlineStr"/>
+      <c r="U291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -25828,8 +25912,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F292" s="4" t="inlineStr"/>
-      <c r="G292" s="4" t="inlineStr"/>
+      <c r="F292" s="4" t="n"/>
+      <c r="G292" s="4" t="n"/>
       <c r="H292" s="4" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -25889,7 +25973,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U292" s="4" t="inlineStr"/>
+      <c r="U292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -25917,8 +26001,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F293" s="4" t="inlineStr"/>
-      <c r="G293" s="4" t="inlineStr"/>
+      <c r="F293" s="4" t="n"/>
+      <c r="G293" s="4" t="n"/>
       <c r="H293" s="4" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -25978,7 +26062,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U293" s="4" t="inlineStr"/>
+      <c r="U293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -26006,8 +26090,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F294" s="4" t="inlineStr"/>
-      <c r="G294" s="4" t="inlineStr"/>
+      <c r="F294" s="4" t="n"/>
+      <c r="G294" s="4" t="n"/>
       <c r="H294" s="4" t="inlineStr">
         <is>
           <t>케이엠테크</t>
@@ -26067,7 +26151,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U294" s="4" t="inlineStr"/>
+      <c r="U294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -26095,7 +26179,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F295" s="4" t="inlineStr"/>
+      <c r="F295" s="4" t="n"/>
       <c r="G295" s="4" t="n">
         <v>11000000</v>
       </c>
@@ -26158,7 +26242,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U295" s="4" t="inlineStr"/>
+      <c r="U295" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -26171,7 +26259,7 @@
           <t>알마이트3T</t>
         </is>
       </c>
-      <c r="C296" s="4" t="inlineStr"/>
+      <c r="C296" s="4" t="n"/>
       <c r="D296" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -26182,9 +26270,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F296" s="4" t="inlineStr"/>
-      <c r="G296" s="4" t="inlineStr"/>
-      <c r="H296" s="4" t="inlineStr"/>
+      <c r="F296" s="4" t="n"/>
+      <c r="G296" s="4" t="n"/>
+      <c r="H296" s="4" t="n"/>
       <c r="I296" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26239,7 +26327,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U296" s="4" t="inlineStr"/>
+      <c r="U296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -26252,7 +26340,7 @@
           <t>스카시30T</t>
         </is>
       </c>
-      <c r="C297" s="4" t="inlineStr"/>
+      <c r="C297" s="4" t="n"/>
       <c r="D297" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -26263,9 +26351,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F297" s="4" t="inlineStr"/>
-      <c r="G297" s="4" t="inlineStr"/>
-      <c r="H297" s="4" t="inlineStr"/>
+      <c r="F297" s="4" t="n"/>
+      <c r="G297" s="4" t="n"/>
+      <c r="H297" s="4" t="n"/>
       <c r="I297" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26320,7 +26408,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U297" s="4" t="inlineStr"/>
+      <c r="U297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -26333,7 +26421,7 @@
           <t>스카시50T</t>
         </is>
       </c>
-      <c r="C298" s="4" t="inlineStr"/>
+      <c r="C298" s="4" t="n"/>
       <c r="D298" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -26344,9 +26432,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F298" s="4" t="inlineStr"/>
-      <c r="G298" s="4" t="inlineStr"/>
-      <c r="H298" s="4" t="inlineStr"/>
+      <c r="F298" s="4" t="n"/>
+      <c r="G298" s="4" t="n"/>
+      <c r="H298" s="4" t="n"/>
       <c r="I298" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26401,7 +26489,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U298" s="4" t="inlineStr"/>
+      <c r="U298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -26414,7 +26502,7 @@
           <t>아크릴 2T</t>
         </is>
       </c>
-      <c r="C299" s="4" t="inlineStr"/>
+      <c r="C299" s="4" t="n"/>
       <c r="D299" s="4" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -26425,9 +26513,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F299" s="4" t="inlineStr"/>
-      <c r="G299" s="4" t="inlineStr"/>
-      <c r="H299" s="4" t="inlineStr"/>
+      <c r="F299" s="4" t="n"/>
+      <c r="G299" s="4" t="n"/>
+      <c r="H299" s="4" t="n"/>
       <c r="I299" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26482,7 +26570,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U299" s="4" t="inlineStr"/>
+      <c r="U299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -26495,7 +26583,7 @@
           <t>아크릴 3T</t>
         </is>
       </c>
-      <c r="C300" s="4" t="inlineStr"/>
+      <c r="C300" s="4" t="n"/>
       <c r="D300" s="4" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -26506,9 +26594,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F300" s="4" t="inlineStr"/>
-      <c r="G300" s="4" t="inlineStr"/>
-      <c r="H300" s="4" t="inlineStr"/>
+      <c r="F300" s="4" t="n"/>
+      <c r="G300" s="4" t="n"/>
+      <c r="H300" s="4" t="n"/>
       <c r="I300" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26563,7 +26651,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U300" s="4" t="inlineStr"/>
+      <c r="U300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -26576,7 +26664,7 @@
           <t>아크릴 5T</t>
         </is>
       </c>
-      <c r="C301" s="4" t="inlineStr"/>
+      <c r="C301" s="4" t="n"/>
       <c r="D301" s="4" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -26587,9 +26675,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F301" s="4" t="inlineStr"/>
-      <c r="G301" s="4" t="inlineStr"/>
-      <c r="H301" s="4" t="inlineStr"/>
+      <c r="F301" s="4" t="n"/>
+      <c r="G301" s="4" t="n"/>
+      <c r="H301" s="4" t="n"/>
       <c r="I301" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26644,7 +26732,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U301" s="4" t="inlineStr"/>
+      <c r="U301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -26657,7 +26745,7 @@
           <t>돼지표본드</t>
         </is>
       </c>
-      <c r="C302" s="4" t="inlineStr"/>
+      <c r="C302" s="4" t="n"/>
       <c r="D302" s="4" t="inlineStr">
         <is>
           <t>[원재료]</t>
@@ -26668,9 +26756,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F302" s="4" t="inlineStr"/>
-      <c r="G302" s="4" t="inlineStr"/>
-      <c r="H302" s="4" t="inlineStr"/>
+      <c r="F302" s="4" t="n"/>
+      <c r="G302" s="4" t="n"/>
+      <c r="H302" s="4" t="n"/>
       <c r="I302" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26725,7 +26813,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U302" s="4" t="inlineStr"/>
+      <c r="U302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -26753,8 +26841,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F303" s="4" t="inlineStr"/>
-      <c r="G303" s="4" t="inlineStr"/>
+      <c r="F303" s="4" t="n"/>
+      <c r="G303" s="4" t="n"/>
       <c r="H303" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -26814,7 +26902,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U303" s="4" t="inlineStr"/>
+      <c r="U303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -26842,9 +26930,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F304" s="4" t="inlineStr"/>
-      <c r="G304" s="4" t="inlineStr"/>
-      <c r="H304" s="4" t="inlineStr"/>
+      <c r="F304" s="4" t="n"/>
+      <c r="G304" s="4" t="n"/>
+      <c r="H304" s="4" t="n"/>
       <c r="I304" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26899,7 +26987,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U304" s="4" t="inlineStr"/>
+      <c r="U304" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -26927,9 +27019,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F305" s="4" t="inlineStr"/>
-      <c r="G305" s="4" t="inlineStr"/>
-      <c r="H305" s="4" t="inlineStr"/>
+      <c r="F305" s="4" t="n"/>
+      <c r="G305" s="4" t="n"/>
+      <c r="H305" s="4" t="n"/>
       <c r="I305" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -26984,7 +27076,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U305" s="4" t="inlineStr"/>
+      <c r="U305" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -27012,9 +27108,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F306" s="4" t="inlineStr"/>
-      <c r="G306" s="4" t="inlineStr"/>
-      <c r="H306" s="4" t="inlineStr"/>
+      <c r="F306" s="4" t="n"/>
+      <c r="G306" s="4" t="n"/>
+      <c r="H306" s="4" t="n"/>
       <c r="I306" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -27069,7 +27165,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U306" s="4" t="inlineStr"/>
+      <c r="U306" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -27097,9 +27197,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F307" s="4" t="inlineStr"/>
-      <c r="G307" s="4" t="inlineStr"/>
-      <c r="H307" s="4" t="inlineStr"/>
+      <c r="F307" s="4" t="n"/>
+      <c r="G307" s="4" t="n"/>
+      <c r="H307" s="4" t="n"/>
       <c r="I307" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -27154,7 +27254,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U307" s="4" t="inlineStr"/>
+      <c r="U307" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -27182,9 +27286,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F308" s="4" t="inlineStr"/>
-      <c r="G308" s="4" t="inlineStr"/>
-      <c r="H308" s="4" t="inlineStr"/>
+      <c r="F308" s="4" t="n"/>
+      <c r="G308" s="4" t="n"/>
+      <c r="H308" s="4" t="n"/>
       <c r="I308" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -27239,7 +27343,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U308" s="4" t="inlineStr"/>
+      <c r="U308" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -27267,8 +27375,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F309" s="4" t="inlineStr"/>
-      <c r="G309" s="4" t="inlineStr"/>
+      <c r="F309" s="4" t="n"/>
+      <c r="G309" s="4" t="n"/>
       <c r="H309" s="4" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -27328,7 +27436,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U309" s="4" t="inlineStr"/>
+      <c r="U309" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -27356,8 +27468,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F310" s="4" t="inlineStr"/>
-      <c r="G310" s="4" t="inlineStr"/>
+      <c r="F310" s="4" t="n"/>
+      <c r="G310" s="4" t="n"/>
       <c r="H310" s="4" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -27417,7 +27529,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U310" s="4" t="inlineStr"/>
+      <c r="U310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -27445,8 +27557,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F311" s="4" t="inlineStr"/>
-      <c r="G311" s="4" t="inlineStr"/>
+      <c r="F311" s="4" t="n"/>
+      <c r="G311" s="4" t="n"/>
       <c r="H311" s="4" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -27506,7 +27618,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U311" s="4" t="inlineStr"/>
+      <c r="U311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -27534,8 +27646,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F312" s="4" t="inlineStr"/>
-      <c r="G312" s="4" t="inlineStr"/>
+      <c r="F312" s="4" t="n"/>
+      <c r="G312" s="4" t="n"/>
       <c r="H312" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -27595,7 +27707,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U312" s="4" t="inlineStr"/>
+      <c r="U312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -27623,8 +27735,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F313" s="4" t="inlineStr"/>
-      <c r="G313" s="4" t="inlineStr"/>
+      <c r="F313" s="4" t="n"/>
+      <c r="G313" s="4" t="n"/>
       <c r="H313" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -27684,7 +27796,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U313" s="4" t="inlineStr"/>
+      <c r="U313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -27712,9 +27824,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F314" s="4" t="inlineStr"/>
-      <c r="G314" s="4" t="inlineStr"/>
-      <c r="H314" s="4" t="inlineStr"/>
+      <c r="F314" s="4" t="n"/>
+      <c r="G314" s="4" t="n"/>
+      <c r="H314" s="4" t="n"/>
       <c r="I314" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -27769,7 +27881,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U314" s="4" t="inlineStr"/>
+      <c r="U314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -27797,7 +27909,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F315" s="4" t="inlineStr"/>
+      <c r="F315" s="4" t="n"/>
       <c r="G315" s="4" t="n">
         <v>54000</v>
       </c>
@@ -27860,7 +27972,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U315" s="4" t="inlineStr"/>
+      <c r="U315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -27888,7 +28000,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F316" s="4" t="inlineStr"/>
+      <c r="F316" s="4" t="n"/>
       <c r="G316" s="4" t="n">
         <v>70000</v>
       </c>
@@ -27951,7 +28063,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U316" s="4" t="inlineStr"/>
+      <c r="U316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -27979,7 +28091,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F317" s="4" t="inlineStr"/>
+      <c r="F317" s="4" t="n"/>
       <c r="G317" s="4" t="n">
         <v>87000</v>
       </c>
@@ -28042,7 +28154,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U317" s="4" t="inlineStr"/>
+      <c r="U317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -28070,7 +28182,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F318" s="4" t="inlineStr"/>
+      <c r="F318" s="4" t="n"/>
       <c r="G318" s="4" t="n">
         <v>54000</v>
       </c>
@@ -28133,7 +28245,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U318" s="4" t="inlineStr"/>
+      <c r="U318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -28161,7 +28273,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F319" s="4" t="inlineStr"/>
+      <c r="F319" s="4" t="n"/>
       <c r="G319" s="4" t="n">
         <v>87000</v>
       </c>
@@ -28224,7 +28336,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U319" s="4" t="inlineStr"/>
+      <c r="U319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -28252,8 +28364,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F320" s="4" t="inlineStr"/>
-      <c r="G320" s="4" t="inlineStr"/>
+      <c r="F320" s="4" t="n"/>
+      <c r="G320" s="4" t="n"/>
       <c r="H320" s="4" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -28313,7 +28425,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U320" s="4" t="inlineStr"/>
+      <c r="U320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -28341,8 +28453,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F321" s="4" t="inlineStr"/>
-      <c r="G321" s="4" t="inlineStr"/>
+      <c r="F321" s="4" t="n"/>
+      <c r="G321" s="4" t="n"/>
       <c r="H321" s="4" t="inlineStr">
         <is>
           <t>아누코</t>
@@ -28402,7 +28514,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U321" s="4" t="inlineStr"/>
+      <c r="U321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -28430,8 +28542,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F322" s="4" t="inlineStr"/>
-      <c r="G322" s="4" t="inlineStr"/>
+      <c r="F322" s="4" t="n"/>
+      <c r="G322" s="4" t="n"/>
       <c r="H322" s="4" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -28491,7 +28603,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U322" s="4" t="inlineStr"/>
+      <c r="U322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -28519,8 +28631,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F323" s="4" t="inlineStr"/>
-      <c r="G323" s="4" t="inlineStr"/>
+      <c r="F323" s="4" t="n"/>
+      <c r="G323" s="4" t="n"/>
       <c r="H323" s="4" t="inlineStr">
         <is>
           <t>(주)엘이디포유</t>
@@ -28580,7 +28692,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U323" s="4" t="inlineStr"/>
+      <c r="U323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -28608,8 +28720,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F324" s="4" t="inlineStr"/>
-      <c r="G324" s="4" t="inlineStr"/>
+      <c r="F324" s="4" t="n"/>
+      <c r="G324" s="4" t="n"/>
       <c r="H324" s="4" t="inlineStr">
         <is>
           <t>(주)티피엠</t>
@@ -28669,7 +28781,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U324" s="4" t="inlineStr"/>
+      <c r="U324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -28697,8 +28809,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F325" s="4" t="inlineStr"/>
-      <c r="G325" s="4" t="inlineStr"/>
+      <c r="F325" s="4" t="n"/>
+      <c r="G325" s="4" t="n"/>
       <c r="H325" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -28758,7 +28870,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U325" s="4" t="inlineStr"/>
+      <c r="U325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -28771,7 +28883,7 @@
           <t>철제배너 부속SET-TSO</t>
         </is>
       </c>
-      <c r="C326" s="4" t="inlineStr"/>
+      <c r="C326" s="4" t="n"/>
       <c r="D326" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -28782,8 +28894,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F326" s="4" t="inlineStr"/>
-      <c r="G326" s="4" t="inlineStr"/>
+      <c r="F326" s="4" t="n"/>
+      <c r="G326" s="4" t="n"/>
       <c r="H326" s="4" t="inlineStr">
         <is>
           <t>사인데코</t>
@@ -28843,7 +28955,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U326" s="4" t="inlineStr"/>
+      <c r="U326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -28871,8 +28983,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F327" s="4" t="inlineStr"/>
-      <c r="G327" s="4" t="inlineStr"/>
+      <c r="F327" s="4" t="n"/>
+      <c r="G327" s="4" t="n"/>
       <c r="H327" s="4" t="inlineStr">
         <is>
           <t>더싸인</t>
@@ -28932,7 +29044,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U327" s="4" t="inlineStr"/>
+      <c r="U327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -28945,7 +29057,7 @@
           <t>간판채널</t>
         </is>
       </c>
-      <c r="C328" s="4" t="inlineStr"/>
+      <c r="C328" s="4" t="n"/>
       <c r="D328" s="4" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -28956,9 +29068,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F328" s="4" t="inlineStr"/>
-      <c r="G328" s="4" t="inlineStr"/>
-      <c r="H328" s="4" t="inlineStr"/>
+      <c r="F328" s="4" t="n"/>
+      <c r="G328" s="4" t="n"/>
+      <c r="H328" s="4" t="n"/>
       <c r="I328" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29013,7 +29125,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U328" s="4" t="inlineStr"/>
+      <c r="U328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -29026,7 +29138,7 @@
           <t>자이언트배너 출력</t>
         </is>
       </c>
-      <c r="C329" s="4" t="inlineStr"/>
+      <c r="C329" s="4" t="n"/>
       <c r="D329" s="4" t="inlineStr">
         <is>
           <t>[제품]</t>
@@ -29037,9 +29149,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F329" s="4" t="inlineStr"/>
-      <c r="G329" s="4" t="inlineStr"/>
-      <c r="H329" s="4" t="inlineStr"/>
+      <c r="F329" s="4" t="n"/>
+      <c r="G329" s="4" t="n"/>
+      <c r="H329" s="4" t="n"/>
       <c r="I329" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29094,7 +29206,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U329" s="4" t="inlineStr"/>
+      <c r="U329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -29122,8 +29234,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F330" s="4" t="inlineStr"/>
-      <c r="G330" s="4" t="inlineStr"/>
+      <c r="F330" s="4" t="n"/>
+      <c r="G330" s="4" t="n"/>
       <c r="H330" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -29183,7 +29295,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U330" s="4" t="inlineStr"/>
+      <c r="U330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -29211,8 +29323,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F331" s="4" t="inlineStr"/>
-      <c r="G331" s="4" t="inlineStr"/>
+      <c r="F331" s="4" t="n"/>
+      <c r="G331" s="4" t="n"/>
       <c r="H331" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -29272,7 +29384,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U331" s="4" t="inlineStr"/>
+      <c r="U331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -29300,9 +29412,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F332" s="4" t="inlineStr"/>
-      <c r="G332" s="4" t="inlineStr"/>
-      <c r="H332" s="4" t="inlineStr"/>
+      <c r="F332" s="4" t="n"/>
+      <c r="G332" s="4" t="n"/>
+      <c r="H332" s="4" t="n"/>
       <c r="I332" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29357,7 +29469,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U332" s="4" t="inlineStr"/>
+      <c r="U332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -29385,9 +29497,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F333" s="4" t="inlineStr"/>
-      <c r="G333" s="4" t="inlineStr"/>
-      <c r="H333" s="4" t="inlineStr"/>
+      <c r="F333" s="4" t="n"/>
+      <c r="G333" s="4" t="n"/>
+      <c r="H333" s="4" t="n"/>
       <c r="I333" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29442,7 +29554,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U333" s="4" t="inlineStr"/>
+      <c r="U333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -29470,9 +29582,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F334" s="4" t="inlineStr"/>
-      <c r="G334" s="4" t="inlineStr"/>
-      <c r="H334" s="4" t="inlineStr"/>
+      <c r="F334" s="4" t="n"/>
+      <c r="G334" s="4" t="n"/>
+      <c r="H334" s="4" t="n"/>
       <c r="I334" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29527,7 +29639,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U334" s="4" t="inlineStr"/>
+      <c r="U334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -29555,8 +29667,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F335" s="4" t="inlineStr"/>
-      <c r="G335" s="4" t="inlineStr"/>
+      <c r="F335" s="4" t="n"/>
+      <c r="G335" s="4" t="n"/>
       <c r="H335" s="4" t="inlineStr">
         <is>
           <t>바로B&amp;R</t>
@@ -29616,7 +29728,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U335" s="4" t="inlineStr"/>
+      <c r="U335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -29644,9 +29756,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F336" s="4" t="inlineStr"/>
-      <c r="G336" s="4" t="inlineStr"/>
-      <c r="H336" s="4" t="inlineStr"/>
+      <c r="F336" s="4" t="n"/>
+      <c r="G336" s="4" t="n"/>
+      <c r="H336" s="4" t="n"/>
       <c r="I336" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29701,7 +29813,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U336" s="4" t="inlineStr"/>
+      <c r="U336" s="4" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
@@ -29729,9 +29841,9 @@
           <t>간판</t>
         </is>
       </c>
-      <c r="F337" s="4" t="inlineStr"/>
-      <c r="G337" s="4" t="inlineStr"/>
-      <c r="H337" s="4" t="inlineStr"/>
+      <c r="F337" s="4" t="n"/>
+      <c r="G337" s="4" t="n"/>
+      <c r="H337" s="4" t="n"/>
       <c r="I337" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -29786,7 +29898,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U337" s="4" t="inlineStr"/>
+      <c r="U337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
@@ -29814,7 +29926,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F338" s="4" t="inlineStr"/>
+      <c r="F338" s="4" t="n"/>
       <c r="G338" s="4" t="n">
         <v>66000</v>
       </c>
@@ -29877,7 +29989,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U338" s="4" t="inlineStr"/>
+      <c r="U338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
@@ -29905,7 +30017,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F339" s="4" t="inlineStr"/>
+      <c r="F339" s="4" t="n"/>
       <c r="G339" s="4" t="n">
         <v>84800</v>
       </c>
@@ -29968,7 +30080,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U339" s="4" t="inlineStr"/>
+      <c r="U339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
@@ -29996,7 +30108,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F340" s="4" t="inlineStr"/>
+      <c r="F340" s="4" t="n"/>
       <c r="G340" s="4" t="n">
         <v>66000</v>
       </c>
@@ -30059,7 +30171,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U340" s="4" t="inlineStr"/>
+      <c r="U340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
@@ -30087,7 +30199,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F341" s="4" t="inlineStr"/>
+      <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n">
         <v>84600</v>
       </c>
@@ -30150,7 +30262,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U341" s="4" t="inlineStr"/>
+      <c r="U341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
@@ -30178,7 +30290,7 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F342" s="4" t="inlineStr"/>
+      <c r="F342" s="4" t="n"/>
       <c r="G342" s="4" t="n">
         <v>72500</v>
       </c>
@@ -30241,7 +30353,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U342" s="4" t="inlineStr"/>
+      <c r="U342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
@@ -30269,8 +30381,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F343" s="4" t="inlineStr"/>
-      <c r="G343" s="4" t="inlineStr"/>
+      <c r="F343" s="4" t="n"/>
+      <c r="G343" s="4" t="n"/>
       <c r="H343" s="4" t="inlineStr">
         <is>
           <t>(주)서울경금속</t>
@@ -30330,7 +30442,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U343" s="4" t="inlineStr"/>
+      <c r="U343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
@@ -30358,8 +30470,8 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F344" s="4" t="inlineStr"/>
-      <c r="G344" s="4" t="inlineStr"/>
+      <c r="F344" s="4" t="n"/>
+      <c r="G344" s="4" t="n"/>
       <c r="H344" s="4" t="inlineStr">
         <is>
           <t>(주)우림테크</t>
@@ -30419,7 +30531,7 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U344" s="4" t="inlineStr"/>
+      <c r="U344" s="4" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
@@ -30447,9 +30559,9 @@
           <t>영업부</t>
         </is>
       </c>
-      <c r="F345" s="4" t="inlineStr"/>
-      <c r="G345" s="4" t="inlineStr"/>
-      <c r="H345" s="4" t="inlineStr"/>
+      <c r="F345" s="4" t="n"/>
+      <c r="G345" s="4" t="n"/>
+      <c r="H345" s="4" t="n"/>
       <c r="I345" s="4" t="inlineStr">
         <is>
           <t>단가 없음</t>
@@ -30504,10 +30616,11 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="U345" s="4" t="inlineStr"/>
+      <c r="U345" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U345"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>